--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.51566739822057</v>
+        <v>5.446295952210843</v>
       </c>
       <c r="D2" t="n">
-        <v>33.87088503131472</v>
+        <v>5.504018817588642</v>
       </c>
       <c r="E2" t="n">
-        <v>12.56108299003073</v>
+        <v>2.041175985879994</v>
       </c>
       <c r="F2" t="n">
-        <v>12.94451942662516</v>
+        <v>2.103484406826588</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.68732125407565</v>
+        <v>7.586689703787293</v>
       </c>
       <c r="D3" t="n">
-        <v>45.35867510855047</v>
+        <v>7.370784705139452</v>
       </c>
       <c r="E3" t="n">
-        <v>12.56108299003073</v>
+        <v>2.041175985879994</v>
       </c>
       <c r="F3" t="n">
-        <v>12.94451942662516</v>
+        <v>2.103484406826588</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9.399234439856015</v>
+        <v>1.527375596476602</v>
       </c>
       <c r="D4" t="n">
-        <v>9.637418699073306</v>
+        <v>1.566080538599412</v>
       </c>
       <c r="E4" t="n">
-        <v>12.56108299003073</v>
+        <v>2.041175985879994</v>
       </c>
       <c r="F4" t="n">
-        <v>12.94451942662516</v>
+        <v>2.103484406826588</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.58350613771262</v>
+        <v>5.457319747378301</v>
       </c>
       <c r="D5" t="n">
-        <v>33.82795106136462</v>
+        <v>5.497042047471751</v>
       </c>
       <c r="E5" t="n">
-        <v>12.56108299003073</v>
+        <v>2.041175985879994</v>
       </c>
       <c r="F5" t="n">
-        <v>12.94451942662516</v>
+        <v>2.103484406826588</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.00324737173459</v>
+        <v>5.688027697906871</v>
       </c>
       <c r="D6" t="n">
-        <v>24.10580842867544</v>
+        <v>3.917193869659759</v>
       </c>
       <c r="E6" t="n">
-        <v>12.56108299003073</v>
+        <v>2.041175985879994</v>
       </c>
       <c r="F6" t="n">
-        <v>12.94451942662516</v>
+        <v>2.103484406826588</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>53.00782138493181</v>
+        <v>8.61377097505142</v>
       </c>
       <c r="D7" t="n">
-        <v>52.26657490935909</v>
+        <v>8.493318422770852</v>
       </c>
       <c r="E7" t="n">
-        <v>12.56108299003073</v>
+        <v>2.041175985879994</v>
       </c>
       <c r="F7" t="n">
-        <v>12.94451942662516</v>
+        <v>2.103484406826588</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>39.76706035613172</v>
+        <v>6.462147307871405</v>
       </c>
       <c r="D8" t="n">
-        <v>39.50752354850817</v>
+        <v>6.419972576632578</v>
       </c>
       <c r="E8" t="n">
-        <v>12.56108299003073</v>
+        <v>2.041175985879994</v>
       </c>
       <c r="F8" t="n">
-        <v>12.94451942662516</v>
+        <v>2.103484406826588</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>47.7620549299055</v>
+        <v>7.761333926109645</v>
       </c>
       <c r="D9" t="n">
-        <v>47.43599024953804</v>
+        <v>7.708348415549932</v>
       </c>
       <c r="E9" t="n">
-        <v>12.56108299003073</v>
+        <v>2.041175985879994</v>
       </c>
       <c r="F9" t="n">
-        <v>12.94451942662516</v>
+        <v>2.103484406826588</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
